--- a/artfynd/A 43777-2022 artfynd.xlsx
+++ b/artfynd/A 43777-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43777-2022 artfynd.xlsx
+++ b/artfynd/A 43777-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY156"/>
+  <dimension ref="A1:AZ156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109149</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110550</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111096656</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111097023</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111097720</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111097767</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105855</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105856</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105857</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1671,6 +1721,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105858</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1772,6 +1827,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105859</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,6 +1933,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105860</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105861</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105862</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2176,6 +2251,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105863</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2277,6 +2357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105864</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2378,6 +2463,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105865</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2479,6 +2569,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105867</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105868</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2681,6 +2781,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105869</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2782,6 +2887,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105871</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2883,6 +2993,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105872</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2984,6 +3099,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105873</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3085,6 +3205,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105874</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3186,6 +3311,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109116</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3287,6 +3417,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109118</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3388,6 +3523,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109119</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3489,6 +3629,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109120</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3590,6 +3735,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109121</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3691,6 +3841,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109123</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3792,6 +3947,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110419</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3893,6 +4053,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109107</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3994,6 +4159,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110551</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4095,6 +4265,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110599</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4229,6 +4404,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113043276</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4330,6 +4510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109043</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4463,6 +4648,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110561</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4561,6 +4751,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111096536</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4662,6 +4857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105790</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4763,6 +4963,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110545</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4861,6 +5066,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111097254</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4959,6 +5169,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111097808</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5057,6 +5272,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111098572</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5158,6 +5378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105885</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5259,6 +5484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106448</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5360,6 +5590,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109131</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5461,6 +5696,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110744</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5562,6 +5802,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112315</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5663,6 +5908,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105772</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5764,6 +6014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110707</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5865,6 +6120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112104</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5966,6 +6226,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112105</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6065,6 +6330,11 @@
       <c r="AY54" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112106</t>
         </is>
       </c>
     </row>
@@ -6196,6 +6466,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113043279</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6297,6 +6572,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110556</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6398,6 +6678,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112122</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6499,6 +6784,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109148</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6600,6 +6890,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112317</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6701,6 +6996,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112318</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6799,6 +7099,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111096675</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6897,6 +7202,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111098213</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6998,6 +7308,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105822</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7099,6 +7414,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105823</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7200,6 +7520,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105824</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7301,6 +7626,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105825</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7402,6 +7732,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105826</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7503,6 +7838,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106428</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7604,6 +7944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106429</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7705,6 +8050,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109087</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7806,6 +8156,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109089</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7907,6 +8262,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109090</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8008,6 +8368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109092</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8109,6 +8474,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110553</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8210,6 +8580,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110558</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8311,6 +8686,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112139</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8412,6 +8792,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112140</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8513,6 +8898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112141</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8614,6 +9004,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112303</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8715,6 +9110,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112304</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8816,6 +9216,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112305</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8917,6 +9322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112306</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9018,6 +9428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112307</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9116,6 +9531,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111096668</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9217,6 +9637,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105773</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9318,6 +9743,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106398</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9419,6 +9849,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109037</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9530,6 +9965,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110661</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9631,6 +10071,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112107</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9732,6 +10177,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112108</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9833,6 +10283,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112276</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9934,6 +10389,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112277</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10035,6 +10495,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112278</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10136,6 +10601,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112280</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10239,6 +10709,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111098286</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10340,6 +10815,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106425</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10441,6 +10921,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106449</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10542,6 +11027,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109143</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10643,6 +11133,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110547</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10754,6 +11249,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110665</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10855,6 +11355,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110746</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10963,6 +11468,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111097291</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11064,6 +11574,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106407</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11165,6 +11680,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106408</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11279,6 +11799,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110708</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11388,6 +11913,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109046</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11508,6 +12038,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110617</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11611,6 +12146,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111097267</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11714,6 +12254,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111097721</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11817,6 +12362,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111097955</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11918,6 +12468,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105786</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12019,6 +12574,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109047</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12117,6 +12677,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111099608</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12215,6 +12780,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111098324</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12313,6 +12883,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111096678</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12414,6 +12989,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105800</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12515,6 +13095,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105801</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12616,6 +13201,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105802</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12717,6 +13307,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105803</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12818,6 +13413,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106412</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12919,6 +13519,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106418</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13020,6 +13625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106419</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13121,6 +13731,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106420</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13222,6 +13837,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106421</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13323,6 +13943,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110555</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13424,6 +14049,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110560</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13525,6 +14155,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110718</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13626,6 +14261,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110719</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13727,6 +14367,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112125</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13828,6 +14473,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112126</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13929,6 +14579,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112127</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14030,6 +14685,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112129</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14131,6 +14791,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112288</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14232,6 +14897,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112289</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14333,6 +15003,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112290</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14434,6 +15109,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112291</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14535,6 +15215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112293</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14636,6 +15321,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112294</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14737,6 +15427,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112295</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14838,6 +15533,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112296</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14939,6 +15639,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112320</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15037,6 +15742,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111096475</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15138,6 +15848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105779</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15239,6 +15954,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105780</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15340,6 +16060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105781</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15441,6 +16166,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105782</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15542,6 +16272,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111105783</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15643,6 +16378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106401</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15744,6 +16484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106402</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15845,6 +16590,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111106403</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -15946,6 +16696,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109039</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16047,6 +16802,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111109040</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16148,6 +16908,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110548</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16259,6 +17024,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111110662</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16360,6 +17130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112114</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16461,8 +17236,170 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2023 Jämtlands län + Västernorrlands län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111112115</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>